--- a/engine/adib_study/ADIB_Valuation_Model_10092026.xlsx
+++ b/engine/adib_study/ADIB_Valuation_Model_10092026.xlsx
@@ -1967,10 +1967,10 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>39.4647</v>
+        <v>45.4655</v>
       </c>
       <c r="C3" s="9" t="n">
-        <v>-0.112375</v>
+        <v>-0.110744</v>
       </c>
     </row>
     <row r="4">
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>49.4573</v>
+        <v>56.7896</v>
       </c>
       <c r="C4" s="9" t="n">
-        <v>0.112375</v>
+        <v>0.110744</v>
       </c>
     </row>
     <row r="5">
@@ -1993,10 +1993,10 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>34.569</v>
+        <v>39.9423</v>
       </c>
       <c r="C5" s="9" t="n">
-        <v>-0.222486</v>
+        <v>-0.218771</v>
       </c>
     </row>
     <row r="6">
@@ -2006,10 +2006,10 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>54.3529</v>
+        <v>62.3128</v>
       </c>
       <c r="C6" s="9" t="n">
-        <v>0.222486</v>
+        <v>0.218771</v>
       </c>
     </row>
     <row r="7">
@@ -2019,10 +2019,10 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>36.0034</v>
+        <v>41.5642</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>-0.190225</v>
+        <v>-0.18705</v>
       </c>
     </row>
     <row r="8">
@@ -2032,10 +2032,10 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>52.9186</v>
+        <v>60.6909</v>
       </c>
       <c r="C8" s="9" t="n">
-        <v>0.190225</v>
+        <v>0.18705</v>
       </c>
     </row>
     <row r="9">
@@ -2045,10 +2045,10 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>38.7004</v>
+        <v>43.8477</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>-0.129564</v>
+        <v>-0.142387</v>
       </c>
     </row>
     <row r="10">
@@ -2058,10 +2058,10 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>50.9691</v>
+        <v>59.3838</v>
       </c>
       <c r="C10" s="9" t="n">
-        <v>0.146378</v>
+        <v>0.161483</v>
       </c>
     </row>
     <row r="11">
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>36.6044</v>
+        <v>41.0604</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>-0.176707</v>
+        <v>-0.196903</v>
       </c>
     </row>
     <row r="12">
@@ -2084,10 +2084,10 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>55.9735</v>
+        <v>66.8074</v>
       </c>
       <c r="C12" s="9" t="n">
-        <v>0.258936</v>
+        <v>0.306681</v>
       </c>
     </row>
     <row r="13">
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>46.0776</v>
+        <v>53.7497</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>0.036361</v>
+        <v>0.051286</v>
       </c>
     </row>
     <row r="14">
@@ -2110,10 +2110,10 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>43.0861</v>
+        <v>48.976</v>
       </c>
       <c r="C14" s="9" t="n">
-        <v>-0.030924</v>
+        <v>-0.042082</v>
       </c>
     </row>
     <row r="16">
@@ -4041,7 +4041,7 @@
         </is>
       </c>
       <c r="B26" s="13" t="n">
-        <v>0.105</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
